--- a/task251/golden/count_stations_flagged_2027.xlsx
+++ b/task251/golden/count_stations_flagged_2027.xlsx
@@ -870,19 +870,19 @@
         <v>49</v>
       </c>
       <c r="B6">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C6">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D6">
         <v>7</v>
       </c>
       <c r="E6">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F6">
-        <v>44</v>
+        <v>54</v>
       </c>
     </row>
     <row r="7">
@@ -896,13 +896,13 @@
         <v>20</v>
       </c>
       <c r="D7">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E7">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F7">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="8">
@@ -910,19 +910,19 @@
         <v>11</v>
       </c>
       <c r="B8">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C8">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D8">
         <v>9</v>
       </c>
       <c r="E8">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F8">
-        <v>34</v>
+        <v>37</v>
       </c>
     </row>
     <row r="9">
@@ -930,19 +930,19 @@
         <v>50</v>
       </c>
       <c r="B9" s="5">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="C9" s="5">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D9" s="5">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E9" s="5">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="F9" s="5">
-        <v>127</v>
+        <v>144</v>
       </c>
     </row>
     <row r="10"/>
@@ -976,19 +976,19 @@
         <v>49</v>
       </c>
       <c r="B14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C14">
+        <v>10</v>
+      </c>
+      <c r="D14">
         <v>15</v>
       </c>
-      <c r="D14">
-        <v>9</v>
-      </c>
       <c r="E14">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F14">
-        <v>40</v>
+        <v>48</v>
       </c>
     </row>
     <row r="15">
@@ -996,19 +996,19 @@
         <v>17</v>
       </c>
       <c r="B15">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="C15">
         <v>15</v>
       </c>
       <c r="D15">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E15">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F15">
-        <v>56</v>
+        <v>52</v>
       </c>
     </row>
     <row r="16">
@@ -1019,16 +1019,16 @@
         <v>10</v>
       </c>
       <c r="C16">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D16">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E16">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F16">
-        <v>34</v>
+        <v>53</v>
       </c>
     </row>
     <row r="17">
@@ -1036,19 +1036,19 @@
         <v>50</v>
       </c>
       <c r="B17" s="5">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="C17" s="5">
         <v>37</v>
       </c>
       <c r="D17" s="5">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="E17" s="5">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="F17" s="5">
-        <v>130</v>
+        <v>153</v>
       </c>
     </row>
     <row r="18"/>

--- a/task251/golden/count_stations_flagged_2027.xlsx
+++ b/task251/golden/count_stations_flagged_2027.xlsx
@@ -182,7 +182,7 @@
     <t>Vehicles that passed: each hour's count divided by the station and direction's loops-to-video ratio on its summer validation day (Northline, July and August 2027), by one less the share of vehicles the loops lose at the hour's occupancy and, while the station ran a TCX-2 controller, by one less the share the TCX-2 misses at the day's mean temperature at Halbrook airport. Both are measured on the five Kessel River bridges, where both approaches count the same vehicles: in queued hours the upstream approach counts fewer than the approach past the deck, and on the three bridges with a TCX-2 on one side and a TCX-4 on the other the TCX-2 side falls behind as the days get colder. The validation days were summer weekdays with no queued hour and no cold.</t>
   </si>
   <si>
-    <t>Maintenance visits: days one of Carrick Signal &amp; Systems Ltd.'s technicians was at a station, from the contractor's work orders; controller resets done from the contractor's office are not visits. Power failures: losses of mains power at a station's controller, from the TCX-4 controllers' events and from the breaks in the TCX-2 stations' hourly record; the two controller replacements are not power failures.</t>
+    <t>Maintenance visits: station-days a technician of Carrick Signal &amp; Systems Ltd. attended, from the labour booked to the contractor's work orders; a controller reset sent from the contractor's own premises is not a visit (TDP-03 section 7) and the cabinet door log shows which days the technician was there, including the day either side of an evening call-out that ran past midnight. Power failures: losses of mains power at a station's controller, from the MAINS_FAIL a controller reported and, where the loss stopped the controller, from the break it left in the station's hourly record, with a second loss where the station answered a poll inside the break and failed again; the two controller replacements are not power failures.</t>
   </si>
   <si>
     <t>Stations under their current numbers: R08-01 became R08-05 on 12 May 2027 and R19-01 became R19-03 on 21 September 2027.</t>
